--- a/data/trans_orig/P32B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32B-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2007</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283994</t>
+          <t>283962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122786</t>
+          <t>122103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>410097</t>
+          <t>409608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>416955</t>
+          <t>416946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217874</t>
+          <t>218305</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146901</t>
+          <t>146754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368989</t>
+          <t>368737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376106</t>
+          <t>376125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,62 +1454,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1742</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5945</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6571</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>332198</t>
+          <t>332400</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59867</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>393977</t>
+          <t>394603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17480</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>903</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21210</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>652059</t>
+          <t>651637</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>665182</t>
+          <t>665836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183306</t>
+          <t>183885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191394</t>
+          <t>191422</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>840654</t>
+          <t>839163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>855540</t>
+          <t>855207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210511</t>
+          <t>210737</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133644</t>
+          <t>133522</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>347046</t>
+          <t>346177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>354571</t>
+          <t>354568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133507</t>
+          <t>132870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213987</t>
+          <t>213028</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>350574</t>
+          <t>350240</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>25199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,82 +2806,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4583</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>18108</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>24674</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>15911</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>36824</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>1,33%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>16261</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>24674</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>16622</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>36305</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1850993</t>
+          <t>1850723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1867040</t>
+          <t>1866974</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,82 +2919,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>885189</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>876412</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>889937</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2691</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2745769</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2733619</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>2754532</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>98,67%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>885189</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>878259</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>890459</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2691</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2745769</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2734138</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2753821</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2012</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>15918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277823</t>
+          <t>277549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289853</t>
+          <t>289674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147035</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>149138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>425957</t>
+          <t>425796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>438733</t>
+          <t>438674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8624</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247678</t>
+          <t>249376</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135621</t>
+          <t>135819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>387353</t>
+          <t>387388</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394982</t>
+          <t>394990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28202</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>360018</t>
+          <t>362643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>379484</t>
+          <t>379475</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76443</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78502</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>439667</t>
+          <t>441487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>458316</t>
+          <t>458339</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>34065</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34924</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>630266</t>
+          <t>629724</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>649393</t>
+          <t>649750</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223811</t>
+          <t>224248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>858016</t>
+          <t>858341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>878057</t>
+          <t>878773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>294678</t>
+          <t>294151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302591</t>
+          <t>302373</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178408</t>
+          <t>177568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>475910</t>
+          <t>476193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>486276</t>
+          <t>486440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15631</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125144</t>
+          <t>124426</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135361</t>
+          <t>135290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>255954</t>
+          <t>257487</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>385914</t>
+          <t>384673</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>397578</t>
+          <t>397490</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44512</t>
+          <t>44044</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76288</t>
+          <t>76677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14656</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50303</t>
+          <t>49438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83879</t>
+          <t>82172</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1965016</t>
+          <t>1964627</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1996792</t>
+          <t>1997260</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033056</t>
+          <t>1034058</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1044657</t>
+          <t>1044738</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3005137</t>
+          <t>3006844</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3038713</t>
+          <t>3039578</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2016</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>15610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273143</t>
+          <t>273199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285794</t>
+          <t>286603</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149731</t>
+          <t>149347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>425782</t>
+          <t>427108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>438912</t>
+          <t>439712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229181</t>
+          <t>228962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238065</t>
+          <t>238068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>185892</t>
+          <t>184496</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>419273</t>
+          <t>419497</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>428563</t>
+          <t>428589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318411</t>
+          <t>318798</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329432</t>
+          <t>328641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47585</t>
+          <t>48303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371583</t>
+          <t>370514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>382570</t>
+          <t>382665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>26605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29914</t>
+          <t>30564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632170</t>
+          <t>632193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>650351</t>
+          <t>650153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288191</t>
+          <t>288112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>296654</t>
+          <t>296660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>926539</t>
+          <t>925889</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>944606</t>
+          <t>944440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>303616</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>313866</t>
+          <t>314197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188932</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>494565</t>
+          <t>494754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>504621</t>
+          <t>505113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152820</t>
+          <t>152488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161090</t>
+          <t>161059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244023</t>
+          <t>243800</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251918</t>
+          <t>251864</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>399826</t>
+          <t>400770</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>411227</t>
+          <t>411296</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31091</t>
+          <t>30077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57030</t>
+          <t>56671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39854</t>
+          <t>40081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69706</t>
+          <t>69770</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1939559</t>
+          <t>1939918</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1965498</t>
+          <t>1966512</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1122233</t>
+          <t>1122674</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1135355</t>
+          <t>1135836</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3068694</t>
+          <t>3068630</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3098546</t>
+          <t>3098319</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2023</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2023 (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262679</t>
+          <t>262864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279153</t>
+          <t>279069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157187</t>
+          <t>157231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162248</t>
+          <t>162256</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>424121</t>
+          <t>423823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>440030</t>
+          <t>440093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208686</t>
+          <t>209086</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126569</t>
+          <t>125835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132184</t>
+          <t>132174</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>338163</t>
+          <t>338450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>344525</t>
+          <t>344501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200801</t>
+          <t>201305</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210030</t>
+          <t>210175</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39214</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>241550</t>
+          <t>240170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250520</t>
+          <t>250275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22215</t>
+          <t>22316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24927</t>
+          <t>24855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487561</t>
+          <t>487460</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>503931</t>
+          <t>504209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>407175</t>
+          <t>407298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>898890</t>
+          <t>898962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>917693</t>
+          <t>918006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>13058</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>218237</t>
+          <t>218075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>227897</t>
+          <t>228041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124699</t>
+          <t>124890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130093</t>
+          <t>130142</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346150</t>
+          <t>345736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357200</t>
+          <t>356523</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -10353,97 +10353,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4530</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11404</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2228</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11422</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>10555</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>11196</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205066</t>
+          <t>205707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>20221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45152</t>
+          <t>47255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21668</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>28806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60480</t>
+          <t>59548</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1496407</t>
+          <t>1494304</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1521448</t>
+          <t>1521338</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>981124</t>
+          <t>981425</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>997607</t>
+          <t>997232</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2483871</t>
+          <t>2484803</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2514847</t>
+          <t>2515545</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32B-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283962</t>
+          <t>283995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122103</t>
+          <t>122948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>409608</t>
+          <t>410166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>416946</t>
+          <t>416954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218305</t>
+          <t>217559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146754</t>
+          <t>146283</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368737</t>
+          <t>368968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376125</t>
+          <t>377073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>332400</t>
+          <t>333253</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>394603</t>
+          <t>394262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>651637</t>
+          <t>651746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>665836</t>
+          <t>665239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183885</t>
+          <t>183462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191422</t>
+          <t>191389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>839163</t>
+          <t>840738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>855207</t>
+          <t>856050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210737</t>
+          <t>211355</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133522</t>
+          <t>132762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346177</t>
+          <t>347132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>354568</t>
+          <t>354571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132870</t>
+          <t>133473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213028</t>
+          <t>211305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>350240</t>
+          <t>350264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25199</t>
+          <t>24920</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>15914</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36824</t>
+          <t>36317</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1850723</t>
+          <t>1851002</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1866974</t>
+          <t>1867196</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>876412</t>
+          <t>876913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>889937</t>
+          <t>889594</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2733619</t>
+          <t>2734126</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2754532</t>
+          <t>2754529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15918</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16809</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277549</t>
+          <t>276925</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289674</t>
+          <t>289700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>425796</t>
+          <t>425884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>438674</t>
+          <t>438829</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249376</t>
+          <t>248416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135819</t>
+          <t>134989</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>387388</t>
+          <t>386282</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394990</t>
+          <t>394981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25235</t>
+          <t>25054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>362643</t>
+          <t>362556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>379475</t>
+          <t>379866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>441487</t>
+          <t>441668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>458339</t>
+          <t>458699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34065</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14167</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34599</t>
+          <t>33689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629724</t>
+          <t>629999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>649750</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224248</t>
+          <t>223959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>858341</t>
+          <t>859251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>878773</t>
+          <t>878211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,82 +4755,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2131</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7538</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>6679</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2787</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>13034</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>294151</t>
+          <t>293571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302373</t>
+          <t>302404</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177568</t>
+          <t>177337</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>476193</t>
+          <t>475926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>486440</t>
+          <t>486441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16872</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124426</t>
+          <t>125259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135290</t>
+          <t>135269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257487</t>
+          <t>257082</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>384673</t>
+          <t>383955</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>397490</t>
+          <t>396767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44044</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76677</t>
+          <t>78667</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13654</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49438</t>
+          <t>50176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82172</t>
+          <t>84006</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1964627</t>
+          <t>1962637</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1997260</t>
+          <t>1997170</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1034058</t>
+          <t>1033157</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1044738</t>
+          <t>1044716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3006844</t>
+          <t>3005010</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3039578</t>
+          <t>3038840</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15610</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273199</t>
+          <t>272784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286603</t>
+          <t>285816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149347</t>
+          <t>148558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>427108</t>
+          <t>427415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>439712</t>
+          <t>439635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>228962</t>
+          <t>229269</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238068</t>
+          <t>238072</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184496</t>
+          <t>186252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>419497</t>
+          <t>418984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>428589</t>
+          <t>428556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318798</t>
+          <t>319225</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328641</t>
+          <t>329314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48303</t>
+          <t>48528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>370514</t>
+          <t>371295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>382665</t>
+          <t>382678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26605</t>
+          <t>26555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,47 +7082,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>19229</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>11503</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>30723</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>3,21%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>19229</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>12013</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>30564</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632193</t>
+          <t>632243</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>650153</t>
+          <t>650196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288112</t>
+          <t>289021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>296660</t>
+          <t>296657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,47 +7195,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>937224</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>925730</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>944950</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>96,79%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>937224</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>925889</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>944440</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>303428</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>314197</t>
+          <t>314370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>494754</t>
+          <t>494654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505113</t>
+          <t>505165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14141</t>
+          <t>13868</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152488</t>
+          <t>152715</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161059</t>
+          <t>161077</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243800</t>
+          <t>244201</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251864</t>
+          <t>251943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>400770</t>
+          <t>401043</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30077</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56671</t>
+          <t>58829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40081</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69770</t>
+          <t>70036</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1939918</t>
+          <t>1937760</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1966512</t>
+          <t>1965534</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1122674</t>
+          <t>1121991</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1135836</t>
+          <t>1135081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3068630</t>
+          <t>3068364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3098319</t>
+          <t>3097245</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>19559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>543</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>274188</t>
+          <t>293330</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262864</t>
+          <t>282836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279069</t>
+          <t>299101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>160801</t>
+          <t>173409</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157231</t>
+          <t>169561</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162256</t>
+          <t>174871</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>434987</t>
+          <t>466739</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>423823</t>
+          <t>453776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>440093</t>
+          <t>471949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>281531</t>
+          <t>302395</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>281531</t>
+          <t>302395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>281531</t>
+          <t>302395</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>444274</t>
+          <t>477809</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>444274</t>
+          <t>477809</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>444274</t>
+          <t>477809</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -9089,27 +9089,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>212072</t>
+          <t>223062</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>209086</t>
+          <t>218978</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>130201</t>
+          <t>140211</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>125835</t>
+          <t>135622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132174</t>
+          <t>142919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>342273</t>
+          <t>363273</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>338450</t>
+          <t>358444</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>344501</t>
+          <t>366311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133149</t>
+          <t>144338</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133149</t>
+          <t>144338</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133149</t>
+          <t>144338</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>346113</t>
+          <t>369029</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>346113</t>
+          <t>369029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>346113</t>
+          <t>369029</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>207119</t>
+          <t>221847</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>201305</t>
+          <t>212410</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210175</t>
+          <t>226178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>247452</t>
+          <t>268412</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240170</t>
+          <t>259502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250275</t>
+          <t>272429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>274674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24855</t>
+          <t>26973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>498144</t>
+          <t>532580</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487460</t>
+          <t>523954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>504209</t>
+          <t>537774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>412016</t>
+          <t>225485</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>407298</t>
+          <t>216068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414042</t>
+          <t>228599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>910159</t>
+          <t>758065</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>898962</t>
+          <t>745570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>918006</t>
+          <t>764164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>509776</t>
+          <t>542891</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>509776</t>
+          <t>542891</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>509776</t>
+          <t>542891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>414042</t>
+          <t>229652</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>414042</t>
+          <t>229652</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>414042</t>
+          <t>229652</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>923817</t>
+          <t>772543</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>923817</t>
+          <t>772543</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>923817</t>
+          <t>772543</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13058</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16521</t>
+          <t>18617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>224391</t>
+          <t>248769</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>218075</t>
+          <t>241617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>228041</t>
+          <t>253210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>128352</t>
+          <t>150318</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124890</t>
+          <t>146758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130142</t>
+          <t>152061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>352745</t>
+          <t>399087</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345736</t>
+          <t>391625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356523</t>
+          <t>404056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>256994</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131123</t>
+          <t>153248</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362257</t>
+          <t>410242</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,27 +10496,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>119174</t>
+          <t>124247</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109998</t>
+          <t>114842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10531,27 +10531,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>214034</t>
+          <t>210088</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205707</t>
+          <t>201033</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121402</t>
+          <t>126471</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>35492</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20221</t>
+          <t>23855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47255</t>
+          <t>53011</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21367</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>42701</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>37995</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59548</t>
+          <t>70272</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1510773</t>
+          <t>1605429</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1494304</t>
+          <t>1587910</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1521338</t>
+          <t>1617066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>990877</t>
+          <t>860234</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>981425</t>
+          <t>850379</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>997232</t>
+          <t>866264</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2501650</t>
+          <t>2465663</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2484803</t>
+          <t>2446336</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2515545</t>
+          <t>2478613</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1541559</t>
+          <t>1640921</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1541559</t>
+          <t>1640921</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1541559</t>
+          <t>1640921</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1002792</t>
+          <t>875687</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1002792</t>
+          <t>875687</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1002792</t>
+          <t>875687</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2544351</t>
+          <t>2516608</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2544351</t>
+          <t>2516608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2544351</t>
+          <t>2516608</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
